--- a/reports/analytics/q03_geographic_population_ranking.xlsx
+++ b/reports/analytics/q03_geographic_population_ranking.xlsx
@@ -6156,11 +6156,11 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Oualqadi</t>
+          <t>Tassrirt</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="C442" t="n">
         <v>2954</v>
@@ -6169,11 +6169,11 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Tassrirt</t>
+          <t>Oualqadi</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="C443" t="n">
         <v>2954</v>
